--- a/contacts/12282629379.xlsx
+++ b/contacts/12282629379.xlsx
@@ -1020,7 +1020,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="18.9166666666667" customWidth="1"/>
@@ -1036,7 +1036,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>14074861398</v>
+        <v>14255487136</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1044,7 +1044,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>14059210202</v>
+        <v>18322476361</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -1052,7 +1052,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>18083210267</v>
+        <v>17248166877</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -1060,7 +1060,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>12172483907</v>
+        <v>17064021259</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -1068,7 +1068,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>19257876384</v>
+        <v>16187316456</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -1076,7 +1076,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>15512646664</v>
+        <v>12074757881</v>
       </c>
       <c r="B7">
         <v>6</v>
@@ -1084,7 +1084,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>19372704412</v>
+        <v>15853057446</v>
       </c>
       <c r="B8">
         <v>7</v>
@@ -1092,7 +1092,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>19293210420</v>
+        <v>13088504056</v>
       </c>
       <c r="B9">
         <v>8</v>
@@ -1100,7 +1100,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>15016724056</v>
+        <v>18652352323</v>
       </c>
       <c r="B10">
         <v>9</v>
@@ -1108,7 +1108,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>16145631772</v>
+        <v>16418200140</v>
       </c>
       <c r="B11">
         <v>10</v>
@@ -1116,7 +1116,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>12698152185</v>
+        <v>14147315700</v>
       </c>
       <c r="B12">
         <v>11</v>
@@ -1124,7 +1124,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>15416067947</v>
+        <v>17852491216</v>
       </c>
       <c r="B13">
         <v>12</v>
@@ -1132,7 +1132,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>18125492004</v>
+        <v>17077807172</v>
       </c>
       <c r="B14">
         <v>13</v>
@@ -1140,7 +1140,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>18046614094</v>
+        <v>18505591900</v>
       </c>
       <c r="B15">
         <v>14</v>
@@ -1148,7 +1148,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>13302810996</v>
+        <v>18504590889</v>
       </c>
       <c r="B16">
         <v>15</v>
@@ -1156,7 +1156,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>18702271240</v>
+        <v>12564836239</v>
       </c>
       <c r="B17">
         <v>16</v>
@@ -1164,7 +1164,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>19282776677</v>
+        <v>15059997359</v>
       </c>
       <c r="B18">
         <v>17</v>
@@ -1172,7 +1172,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>19204015213</v>
+        <v>19283007706</v>
       </c>
       <c r="B19">
         <v>18</v>
@@ -1180,7 +1180,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>19545575332</v>
+        <v>13199395504</v>
       </c>
       <c r="B20">
         <v>19</v>
@@ -1188,7 +1188,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>12708417437</v>
+        <v>14345478185</v>
       </c>
       <c r="B21">
         <v>20</v>
@@ -1196,7 +1196,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>16145631772</v>
+        <v>12192697434</v>
       </c>
       <c r="B22">
         <v>21</v>
@@ -1204,7 +1204,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>15152108728</v>
+        <v>16464254487</v>
       </c>
       <c r="B23">
         <v>22</v>
@@ -1212,7 +1212,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>14232273272</v>
+        <v>15722428950</v>
       </c>
       <c r="B24">
         <v>23</v>
@@ -1220,7 +1220,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>17204852701</v>
+        <v>13046427778</v>
       </c>
       <c r="B25">
         <v>24</v>
@@ -1228,10 +1228,50 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>14059018932</v>
+        <v>15412802766</v>
       </c>
       <c r="B26">
         <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>15013669959</v>
+      </c>
+      <c r="B27">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>16467126988</v>
+      </c>
+      <c r="B28">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>15134034130</v>
+      </c>
+      <c r="B29">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>19405073825</v>
+      </c>
+      <c r="B30">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>18602878782</v>
+      </c>
+      <c r="B31">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/contacts/12282629379.xlsx
+++ b/contacts/12282629379.xlsx
@@ -1020,7 +1020,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B70"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="18.9166666666667" customWidth="1"/>
@@ -1036,7 +1036,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>14255487136</v>
+        <v>16398272756</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1044,7 +1044,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>18322476361</v>
+        <v>14069742130</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -1052,7 +1052,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>17248166877</v>
+        <v>13213050377</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -1060,7 +1060,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>17064021259</v>
+        <v>15618917635</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -1068,7 +1068,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>16187316456</v>
+        <v>15403057323</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -1076,7 +1076,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>12074757881</v>
+        <v>16193437758</v>
       </c>
       <c r="B7">
         <v>6</v>
@@ -1084,7 +1084,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>15853057446</v>
+        <v>13239846687</v>
       </c>
       <c r="B8">
         <v>7</v>
@@ -1092,7 +1092,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>13088504056</v>
+        <v>19108016473</v>
       </c>
       <c r="B9">
         <v>8</v>
@@ -1100,7 +1100,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>18652352323</v>
+        <v>13863077494</v>
       </c>
       <c r="B10">
         <v>9</v>
@@ -1108,7 +1108,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>16418200140</v>
+        <v>13189906049</v>
       </c>
       <c r="B11">
         <v>10</v>
@@ -1116,7 +1116,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>14147315700</v>
+        <v>12513690560</v>
       </c>
       <c r="B12">
         <v>11</v>
@@ -1124,7 +1124,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>17852491216</v>
+        <v>14252184450</v>
       </c>
       <c r="B13">
         <v>12</v>
@@ -1132,7 +1132,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>17077807172</v>
+        <v>15303959903</v>
       </c>
       <c r="B14">
         <v>13</v>
@@ -1140,7 +1140,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>18505591900</v>
+        <v>19124290771</v>
       </c>
       <c r="B15">
         <v>14</v>
@@ -1148,7 +1148,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>18504590889</v>
+        <v>12145414001</v>
       </c>
       <c r="B16">
         <v>15</v>
@@ -1156,7 +1156,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>12564836239</v>
+        <v>18065591836</v>
       </c>
       <c r="B17">
         <v>16</v>
@@ -1164,7 +1164,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>15059997359</v>
+        <v>13152781556</v>
       </c>
       <c r="B18">
         <v>17</v>
@@ -1172,7 +1172,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>19283007706</v>
+        <v>15038944090</v>
       </c>
       <c r="B19">
         <v>18</v>
@@ -1180,7 +1180,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>13199395504</v>
+        <v>17868779571</v>
       </c>
       <c r="B20">
         <v>19</v>
@@ -1188,7 +1188,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>14345478185</v>
+        <v>17792679771</v>
       </c>
       <c r="B21">
         <v>20</v>
@@ -1196,23 +1196,20 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>12192697434</v>
+        <v>17144762785</v>
       </c>
       <c r="B22">
         <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23">
-        <v>16464254487</v>
-      </c>
       <c r="B23">
         <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>15722428950</v>
+        <v>17145140494</v>
       </c>
       <c r="B24">
         <v>23</v>
@@ -1220,7 +1217,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>13046427778</v>
+        <v>18014589047</v>
       </c>
       <c r="B25">
         <v>24</v>
@@ -1228,23 +1225,20 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>15412802766</v>
+        <v>13132138314</v>
       </c>
       <c r="B26">
         <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27">
-        <v>15013669959</v>
-      </c>
       <c r="B27">
         <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>16467126988</v>
+        <v>14705584364</v>
       </c>
       <c r="B28">
         <v>27</v>
@@ -1252,7 +1246,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>15134034130</v>
+        <v>15868999582</v>
       </c>
       <c r="B29">
         <v>28</v>
@@ -1260,7 +1254,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>19405073825</v>
+        <v>13785069334</v>
       </c>
       <c r="B30">
         <v>29</v>
@@ -1268,10 +1262,319 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>18602878782</v>
+        <v>18038601598</v>
       </c>
       <c r="B31">
         <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>15172259032</v>
+      </c>
+      <c r="B32">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>18645359082</v>
+      </c>
+      <c r="B33">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>12297266540</v>
+      </c>
+      <c r="B34">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
+        <v>17073501107</v>
+      </c>
+      <c r="B35">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>14143743120</v>
+      </c>
+      <c r="B36">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>14194386949</v>
+      </c>
+      <c r="B37">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>12198402684</v>
+      </c>
+      <c r="B38">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>18705656784</v>
+      </c>
+      <c r="B39">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40">
+        <v>19316383437</v>
+      </c>
+      <c r="B40">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>12707023391</v>
+      </c>
+      <c r="B41">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>14055373886</v>
+      </c>
+      <c r="B42">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="B43">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>18656962204</v>
+      </c>
+      <c r="B44">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>18125282502</v>
+      </c>
+      <c r="B45">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>16027997869</v>
+      </c>
+      <c r="B46">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>12192014515</v>
+      </c>
+      <c r="B47">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>16027526552</v>
+      </c>
+      <c r="B48">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
+        <v>12148134938</v>
+      </c>
+      <c r="B49">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50">
+        <v>18149777176</v>
+      </c>
+      <c r="B50">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51">
+        <v>18436147174</v>
+      </c>
+      <c r="B51">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52">
+        <v>13363450795</v>
+      </c>
+      <c r="B52">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53">
+        <v>12564789060</v>
+      </c>
+      <c r="B53">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54">
+        <v>14844103184</v>
+      </c>
+      <c r="B54">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55">
+        <v>14193045537</v>
+      </c>
+      <c r="B55">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56">
+        <v>16785084784</v>
+      </c>
+      <c r="B56">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57">
+        <v>13049199414</v>
+      </c>
+      <c r="B57">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58">
+        <v>19054144381</v>
+      </c>
+      <c r="B58">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59">
+        <v>19034495601</v>
+      </c>
+      <c r="B59">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60">
+        <v>18052985546</v>
+      </c>
+      <c r="B60">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61">
+        <v>19313830966</v>
+      </c>
+      <c r="B61">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62">
+        <v>13237428714</v>
+      </c>
+      <c r="B62">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63">
+        <v>19189649130</v>
+      </c>
+      <c r="B63">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64">
+        <v>15039017593</v>
+      </c>
+      <c r="B64">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65">
+        <v>12523055141</v>
+      </c>
+      <c r="B65">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66">
+        <v>19109168995</v>
+      </c>
+      <c r="B66">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67">
+        <v>13476983281</v>
+      </c>
+      <c r="B67">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68">
+        <v>19739798283</v>
+      </c>
+      <c r="B68">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69">
+        <v>16198846554</v>
+      </c>
+      <c r="B69">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70">
+        <v>13155213219</v>
+      </c>
+      <c r="B70">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
